--- a/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 10,3</t>
+          <t>-1,78; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 10,25</t>
+          <t>-2,04; 9,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,13; 15,65</t>
+          <t>5,39; 15,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,04; 30,61</t>
+          <t>9,22; 28,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,32; 10,72</t>
+          <t>3,04; 11,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,17; 19,18</t>
+          <t>5,86; 18,19</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-40,09; 720,29</t>
+          <t>-43,98; 626,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,72; 651,5</t>
+          <t>-37,02; 672,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,5; 976,86</t>
+          <t>50,73; 1073,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>132,57; 1556,6</t>
+          <t>131,53; 1577,05</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,61; 11,14</t>
+          <t>1,67; 11,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 19,98</t>
+          <t>7,08; 19,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 10,32</t>
+          <t>-0,07; 10,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 14,67</t>
+          <t>1,35; 14,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 9,06</t>
+          <t>1,59; 8,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,37</t>
+          <t>5,47; 15,19</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-30,81; —</t>
+          <t>-9,89; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>114,9; —</t>
+          <t>140,26; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-18,65; 815,77</t>
+          <t>-13,13; 722,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1010,15</t>
+          <t>9,78; 946,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>31,35; 643,11</t>
+          <t>30,42; 708,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>106,35; 1165,08</t>
+          <t>109,81; 1151,61</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 11,41</t>
+          <t>-1,62; 10,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,27; 26,71</t>
+          <t>7,67; 27,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 16,18</t>
+          <t>2,15; 15,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 21,49</t>
+          <t>2,0; 22,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,61</t>
+          <t>0,93; 11,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,47; 20,1</t>
+          <t>6,95; 20,26</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 635,07</t>
+          <t>-47,1; 666,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85,56; 1630,2</t>
+          <t>80,57; 2162,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1111,68</t>
+          <t>8,85; 1284,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 1394,32</t>
+          <t>-4,06; 1606,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>14,0; 543,55</t>
+          <t>8,01; 476,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>103,1; 923,58</t>
+          <t>112,34; 924,52</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,52; 17,35</t>
+          <t>8,48; 17,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 21,67</t>
+          <t>5,59; 21,49</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,84; 16,2</t>
+          <t>5,8; 15,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 11,39</t>
+          <t>2,33; 12,15</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 14,63</t>
+          <t>8,39; 15,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,49; 14,37</t>
+          <t>5,2; 14,59</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>162,88; 1081,51</t>
+          <t>159,92; 997,41</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>106,2; 1011,52</t>
+          <t>110,19; 1064,54</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>76,96; 448,25</t>
+          <t>72,75; 442,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17,75; 309,63</t>
+          <t>23,97; 321,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>141,58; 450,38</t>
+          <t>145,07; 509,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>98,58; 429,81</t>
+          <t>96,9; 447,98</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 14,64</t>
+          <t>3,41; 14,61</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,73; 16,08</t>
+          <t>2,8; 16,95</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8,15; 19,45</t>
+          <t>7,2; 19,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,52; 17,58</t>
+          <t>4,94; 18,01</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,28</t>
+          <t>6,59; 15,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,5; 14,55</t>
+          <t>5,69; 15,41</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>23,6; 341,18</t>
+          <t>31,61; 321,96</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25,41; 363,37</t>
+          <t>25,94; 384,98</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>101,44; 778,59</t>
+          <t>89,83; 799,56</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>59,62; 688,45</t>
+          <t>63,74; 705,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,11; 394,22</t>
+          <t>84,7; 375,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,75; 384,84</t>
+          <t>73,36; 360,04</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,83; 24,33</t>
+          <t>5,69; 25,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 14,2</t>
+          <t>-2,99; 13,36</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,32; 30,16</t>
+          <t>12,38; 30,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,87; 21,46</t>
+          <t>4,8; 20,79</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,6; 24,56</t>
+          <t>11,9; 24,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,87</t>
+          <t>3,1; 14,83</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7,65; —</t>
+          <t>24,62; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-76,78; —</t>
+          <t>-72,07; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>200,37; 3958,8</t>
+          <t>185,06; 3968,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>29,08; 2618,05</t>
+          <t>7,78; 2009,04</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,51</t>
+          <t>6,72; 11,5</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,01; 13,29</t>
+          <t>6,91; 13,52</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,35</t>
+          <t>8,37; 13,44</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,26</t>
+          <t>7,35; 13,32</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,12; 11,61</t>
+          <t>8,22; 11,73</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,63; 12,34</t>
+          <t>7,7; 12,13</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>144,09; 402,38</t>
+          <t>138,38; 394,94</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>146,7; 440,7</t>
+          <t>149,6; 443,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>187,91; 458,43</t>
+          <t>186,95; 484,57</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>156,75; 449,04</t>
+          <t>157,6; 452,11</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>179,37; 361,98</t>
+          <t>179,32; 375,23</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>173,11; 385,57</t>
+          <t>166,94; 366,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 10,17</t>
+          <t>-0,84; 10,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 9,52</t>
+          <t>-1,05; 9,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 15,69</t>
+          <t>4,88; 15,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 28,4</t>
+          <t>8,94; 31,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,02</t>
+          <t>3,53; 11,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 18,19</t>
+          <t>5,83; 18,49</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,98; 626,71</t>
+          <t>-28,86; 686,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 672,14</t>
+          <t>-34,43; 711,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -725,12 +725,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,73; 1073,37</t>
+          <t>78,29; 1187,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>131,53; 1577,05</t>
+          <t>128,15; 1811,32</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 11,4</t>
+          <t>1,73; 10,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 19,64</t>
+          <t>6,65; 19,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 10,71</t>
+          <t>-0,19; 10,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 14,62</t>
+          <t>1,16; 14,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,85</t>
+          <t>2,2; 9,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,47; 15,19</t>
+          <t>5,87; 15,59</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,89; —</t>
+          <t>4,93; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>140,26; —</t>
+          <t>148,38; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 722,88</t>
+          <t>-15,13; 766,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,78; 946,08</t>
+          <t>-0,68; 1091,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>30,42; 708,28</t>
+          <t>35,9; 673,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>109,81; 1151,61</t>
+          <t>126,98; 1129,65</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 10,42</t>
+          <t>-1,62; 10,28</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 27,46</t>
+          <t>7,66; 27,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 15,91</t>
+          <t>1,82; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 22,55</t>
+          <t>2,3; 22,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 11,03</t>
+          <t>1,51; 11,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,95; 20,26</t>
+          <t>6,86; 20,92</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-47,1; 666,42</t>
+          <t>-50,0; 655,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>80,57; 2162,1</t>
+          <t>97,07; 1706,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,85; 1284,04</t>
+          <t>-1,57; 1386,86</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 1606,26</t>
+          <t>-14,29; 1341,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,01; 476,94</t>
+          <t>19,4; 570,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>112,34; 924,52</t>
+          <t>114,57; 931,03</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 17,87</t>
+          <t>8,39; 16,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,59; 21,49</t>
+          <t>5,73; 20,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,8; 15,33</t>
+          <t>5,78; 16,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 12,15</t>
+          <t>2,06; 11,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,08</t>
+          <t>7,96; 15,09</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,59</t>
+          <t>4,99; 13,87</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>159,92; 997,41</t>
+          <t>165,43; 1023,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>110,19; 1064,54</t>
+          <t>119,32; 1064,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>72,75; 442,66</t>
+          <t>67,63; 435,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,97; 321,04</t>
+          <t>23,09; 318,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>145,07; 509,42</t>
+          <t>132,0; 472,54</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>96,9; 447,98</t>
+          <t>92,01; 417,03</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 14,61</t>
+          <t>2,88; 14,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,8; 16,95</t>
+          <t>2,84; 16,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,2; 19,31</t>
+          <t>7,3; 19,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,94; 18,01</t>
+          <t>5,06; 18,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,59; 15,29</t>
+          <t>6,96; 14,74</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,69; 15,41</t>
+          <t>5,7; 15,09</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>31,61; 321,96</t>
+          <t>27,32; 350,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25,94; 384,98</t>
+          <t>27,36; 377,05</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89,83; 799,56</t>
+          <t>85,95; 955,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63,74; 705,79</t>
+          <t>62,27; 718,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>84,7; 375,32</t>
+          <t>92,87; 386,26</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>73,36; 360,04</t>
+          <t>72,28; 381,35</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5,69; 25,03</t>
+          <t>4,84; 23,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 13,36</t>
+          <t>-3,26; 14,39</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12,38; 30,65</t>
+          <t>13,39; 30,22</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4,8; 20,79</t>
+          <t>5,26; 21,3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,9; 24,2</t>
+          <t>11,73; 24,26</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,1; 14,83</t>
+          <t>3,56; 15,08</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>24,62; —</t>
+          <t>4,31; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-72,07; —</t>
+          <t>-78,17; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1505,12 +1505,12 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>185,06; 3968,36</t>
+          <t>190,22; 3994,39</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,78; 2009,04</t>
+          <t>23,3; 2056,4</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,72; 11,5</t>
+          <t>6,54; 11,3</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,52</t>
+          <t>7,06; 13,68</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,37; 13,44</t>
+          <t>8,29; 13,4</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,32</t>
+          <t>6,68; 13,0</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,22; 11,73</t>
+          <t>8,19; 11,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,7; 12,13</t>
+          <t>7,98; 12,34</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>138,38; 394,94</t>
+          <t>134,53; 383,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>149,6; 443,29</t>
+          <t>149,98; 435,27</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>186,95; 484,57</t>
+          <t>172,18; 468,88</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>157,6; 452,11</t>
+          <t>145,27; 441,29</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>179,32; 375,23</t>
+          <t>180,74; 377,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>166,94; 366,39</t>
+          <t>176,32; 383,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$notiene-Clase-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de calefacción en su vivienda</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9,64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,93</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>4,21</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,11</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9,64</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,3</t>
+          <t>3,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,78</t>
+          <t>7,59</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 10,53</t>
+          <t>5,13; 15,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 9,68</t>
+          <t>6,4; 18,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,88; 15,87</t>
+          <t>-1,6; 10,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,94; 31,33</t>
+          <t>-1,55; 9,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 11,29</t>
+          <t>3,32; 10,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 18,49</t>
+          <t>3,83; 11,8</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1385,26%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1570,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>110,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>107,37%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1385,26%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2340,8%</t>
+          <t>102,97%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>476,52%</t>
+          <t>335,47%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,86; 686,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,43; 711,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-40,09; 720,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-35,96; 661,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>78,29; 1187,32</t>
+          <t>77,5; 976,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>128,15; 1811,32</t>
+          <t>86,8; 1081,52</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>7,49</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>5,95</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>12,49</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7,34</t>
+          <t>12,54</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,88</t>
+          <t>10,03</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,98</t>
+          <t>-0,22; 10,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,65; 19,32</t>
+          <t>1,13; 15,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 10,94</t>
+          <t>1,61; 11,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 14,78</t>
+          <t>6,73; 20,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,4</t>
+          <t>2,02; 9,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,87; 15,59</t>
+          <t>5,9; 15,61</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>141,94%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>206,71%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>402,79%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>845,04%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>141,94%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202,57%</t>
+          <t>848,78%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>383,75%</t>
+          <t>389,55%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,93; —</t>
+          <t>-18,65; 815,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>148,38; —</t>
+          <t>-5,71; 1025,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 766,41</t>
+          <t>-30,81; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1091,42</t>
+          <t>113,85; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,9; 673,76</t>
+          <t>31,35; 643,11</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>126,98; 1129,65</t>
+          <t>110,28; 1198,18</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>8,57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>7,47</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>3,28</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>16,24</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>8,57</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,78</t>
+          <t>15,42</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,68</t>
+          <t>11,32</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 10,28</t>
+          <t>1,28; 16,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,66; 27,93</t>
+          <t>0,59; 16,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 16,84</t>
+          <t>-1,88; 11,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,3; 22,75</t>
+          <t>6,89; 25,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,65</t>
+          <t>1,33; 11,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,86; 20,92</t>
+          <t>5,79; 17,69</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>229,27%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>199,79%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>91,44%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>452,64%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>229,27%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>261,55%</t>
+          <t>429,97%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>346,15%</t>
+          <t>309,13%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-50,0; 655,4</t>
+          <t>-0,21; 1111,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>97,07; 1706,6</t>
+          <t>-21,88; 1207,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 1386,86</t>
+          <t>-59,92; 635,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 1341,2</t>
+          <t>80,46; 1646,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,4; 570,3</t>
+          <t>14,0; 543,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>114,57; 931,03</t>
+          <t>97,64; 843,33</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,59</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>12,64</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>11,96</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,59</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>9,27</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>7,89</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>8,39; 16,78</t>
+          <t>5,84; 16,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,73; 20,55</t>
+          <t>1,85; 11,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,78; 16,11</t>
+          <t>8,52; 17,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,06; 11,78</t>
+          <t>5,15; 14,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,96; 15,09</t>
+          <t>8,07; 14,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,99; 13,87</t>
+          <t>4,91; 11,1</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>193,61%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>121,46%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>413,71%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391,38%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>193,61%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>120,86%</t>
+          <t>303,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>213,45%</t>
+          <t>182,55%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>165,43; 1023,79</t>
+          <t>76,96; 448,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>119,32; 1064,27</t>
+          <t>18,16; 308,24</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>67,63; 435,82</t>
+          <t>162,88; 1081,51</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23,09; 318,43</t>
+          <t>104,87; 833,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>132,0; 472,54</t>
+          <t>141,58; 450,38</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>92,01; 417,03</t>
+          <t>85,94; 349,36</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>13,2</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9,76</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>8,58</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>9,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>13,2</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10,94</t>
+          <t>8,6</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1240,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,88; 14,77</t>
+          <t>8,15; 19,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,84; 16,24</t>
+          <t>3,53; 15,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7,3; 19,95</t>
+          <t>2,47; 14,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,06; 18,35</t>
+          <t>2,47; 15,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>6,96; 14,74</t>
+          <t>6,82; 15,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,7; 15,09</t>
+          <t>5,08; 13,59</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>296,57%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>219,23%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>129,53%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>135,84%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>296,57%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>245,92%</t>
+          <t>129,76%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1316,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>178,39%</t>
+          <t>163,41%</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27,32; 350,83</t>
+          <t>101,44; 778,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>27,36; 377,05</t>
+          <t>42,89; 603,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>85,95; 955,35</t>
+          <t>23,6; 341,18</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62,27; 718,01</t>
+          <t>22,11; 352,34</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,87; 386,26</t>
+          <t>88,11; 394,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>72,28; 381,35</t>
+          <t>68,58; 343,55</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>20,81</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11,22</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>14,84</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>4,9</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20,81</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>11,17</t>
+          <t>2,41</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,32</t>
+          <t>7,02</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,84; 23,93</t>
+          <t>13,32; 30,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 14,39</t>
+          <t>4,89; 21,81</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13,39; 30,22</t>
+          <t>5,83; 24,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,26; 21,3</t>
+          <t>-6,04; 8,22</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>11,73; 24,26</t>
+          <t>12,6; 24,56</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,56; 15,08</t>
+          <t>2,53; 12,45</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2538,58%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1368,56%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>388,39%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>128,26%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>2538,58%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1362,74%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>400,9%</t>
+          <t>338,16%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>4,31; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-78,17; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>7,65; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,27; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>190,22; 3994,39</t>
+          <t>200,37; 3958,8</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,3; 2056,4</t>
+          <t>10,38; 2215,99</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>10,83</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>8,53</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>8,96</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>9,72</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>10,83</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>9,93</t>
+          <t>8,42</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>9,83</t>
+          <t>8,48</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,3</t>
+          <t>8,41; 13,35</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>7,06; 13,68</t>
+          <t>5,96; 11,12</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8,29; 13,4</t>
+          <t>6,6; 11,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6,68; 13,0</t>
+          <t>6,19; 10,95</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>8,19; 11,63</t>
+          <t>8,12; 11,61</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>7,98; 12,34</t>
+          <t>6,74; 10,46</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>290,33%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>228,88%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>232,79%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>252,43%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>290,33%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>266,35%</t>
+          <t>218,72%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>259,52%</t>
+          <t>223,86%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>134,53; 383,55</t>
+          <t>187,91; 458,43</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>149,98; 435,27</t>
+          <t>132,82; 377,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>172,18; 468,88</t>
+          <t>144,09; 402,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>145,27; 441,29</t>
+          <t>127,42; 398,64</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>180,74; 377,72</t>
+          <t>179,37; 361,98</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>176,32; 383,18</t>
+          <t>148,59; 329,82</t>
         </is>
       </c>
     </row>
